--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H611"/>
+  <dimension ref="A1:H614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18748,7 +18748,7 @@
         <v>217.28</v>
       </c>
       <c r="D611" t="n">
-        <v>222.38</v>
+        <v>219.79</v>
       </c>
       <c r="E611" t="n">
         <v>223.72</v>
@@ -18760,6 +18760,96 @@
         <v>210.65</v>
       </c>
       <c r="H611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>213.36</v>
+      </c>
+      <c r="C612" t="n">
+        <v>217.51</v>
+      </c>
+      <c r="D612" t="n">
+        <v>218.21</v>
+      </c>
+      <c r="E612" t="n">
+        <v>224.44</v>
+      </c>
+      <c r="F612" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="G612" t="n">
+        <v>209.91</v>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:12:13+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>213.58</v>
+      </c>
+      <c r="C613" t="n">
+        <v>216.74</v>
+      </c>
+      <c r="D613" t="n">
+        <v>218.87</v>
+      </c>
+      <c r="E613" t="n">
+        <v>226.36</v>
+      </c>
+      <c r="F613" t="n">
+        <v>215.58</v>
+      </c>
+      <c r="G613" t="n">
+        <v>209.59</v>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>213.16</v>
+      </c>
+      <c r="C614" t="n">
+        <v>216.53</v>
+      </c>
+      <c r="D614" t="n">
+        <v>217.32</v>
+      </c>
+      <c r="E614" t="n">
+        <v>224.92</v>
+      </c>
+      <c r="F614" t="n">
+        <v>213.52</v>
+      </c>
+      <c r="G614" t="n">
+        <v>209.93</v>
+      </c>
+      <c r="H614" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18776,7 +18866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25979,6 +26069,56 @@
       </c>
       <c r="B720" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -26141,28 +26281,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1490414657996129</v>
+        <v>-0.1660957204252783</v>
       </c>
       <c r="J2" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K2" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01815834593285592</v>
+        <v>0.02217915487967015</v>
       </c>
       <c r="M2" t="n">
-        <v>5.775937439460368</v>
+        <v>5.819387712809717</v>
       </c>
       <c r="N2" t="n">
-        <v>52.43689783814168</v>
+        <v>53.39493274182521</v>
       </c>
       <c r="O2" t="n">
-        <v>7.241332600988693</v>
+        <v>7.307183639530706</v>
       </c>
       <c r="P2" t="n">
-        <v>233.2140549685087</v>
+        <v>233.4264706041207</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26213,28 +26353,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5186434634232855</v>
+        <v>-0.5217054538269948</v>
       </c>
       <c r="J3" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K3" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2017553609950478</v>
+        <v>0.2052185542059892</v>
       </c>
       <c r="M3" t="n">
-        <v>5.592272740403492</v>
+        <v>5.576582666160881</v>
       </c>
       <c r="N3" t="n">
-        <v>46.46290309562477</v>
+        <v>46.27545639305084</v>
       </c>
       <c r="O3" t="n">
-        <v>6.816370228767271</v>
+        <v>6.802606588143315</v>
       </c>
       <c r="P3" t="n">
-        <v>233.5973686993042</v>
+        <v>233.6355120840051</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26285,28 +26425,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1916176898189056</v>
+        <v>0.1880821721259331</v>
       </c>
       <c r="J4" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K4" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04399344707092223</v>
+        <v>0.04284996916237105</v>
       </c>
       <c r="M4" t="n">
-        <v>4.457485299202788</v>
+        <v>4.445497661943725</v>
       </c>
       <c r="N4" t="n">
-        <v>34.83379398608425</v>
+        <v>34.68857841086513</v>
       </c>
       <c r="O4" t="n">
-        <v>5.902016095037715</v>
+        <v>5.88970104596703</v>
       </c>
       <c r="P4" t="n">
-        <v>215.455414936564</v>
+        <v>215.4994389700358</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26357,28 +26497,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4035488003816147</v>
+        <v>0.4031767241772629</v>
       </c>
       <c r="J5" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K5" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1151166598606842</v>
+        <v>0.1159951715519354</v>
       </c>
       <c r="M5" t="n">
-        <v>5.539798500278975</v>
+        <v>5.516646951299938</v>
       </c>
       <c r="N5" t="n">
-        <v>54.14820708872194</v>
+        <v>53.88658791065538</v>
       </c>
       <c r="O5" t="n">
-        <v>7.358546533706364</v>
+        <v>7.340748457116303</v>
       </c>
       <c r="P5" t="n">
-        <v>214.8318996739743</v>
+        <v>214.8365508844996</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26429,28 +26569,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3123292286271556</v>
+        <v>0.3120348589740151</v>
       </c>
       <c r="J6" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K6" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04189995591391249</v>
+        <v>0.04224473496919512</v>
       </c>
       <c r="M6" t="n">
-        <v>7.557152895941413</v>
+        <v>7.524702594309456</v>
       </c>
       <c r="N6" t="n">
-        <v>96.48652659600569</v>
+        <v>96.0203405221804</v>
       </c>
       <c r="O6" t="n">
-        <v>9.822755550048351</v>
+        <v>9.798996914081584</v>
       </c>
       <c r="P6" t="n">
-        <v>207.0350264279812</v>
+        <v>207.0387237775128</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26501,28 +26641,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2059674258037308</v>
+        <v>-0.2037240486025845</v>
       </c>
       <c r="J7" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K7" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06853834723488361</v>
+        <v>0.06776161786297008</v>
       </c>
       <c r="M7" t="n">
-        <v>3.941862771459186</v>
+        <v>3.932609297743701</v>
       </c>
       <c r="N7" t="n">
-        <v>24.93862795862072</v>
+        <v>24.83721321059429</v>
       </c>
       <c r="O7" t="n">
-        <v>4.993859024704314</v>
+        <v>4.983694734892406</v>
       </c>
       <c r="P7" t="n">
-        <v>213.2249511214107</v>
+        <v>213.1968827961525</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26560,7 +26700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H611"/>
+  <dimension ref="A1:H614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52185,7 +52325,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>-36.89586469901062,174.9878630301108</t>
+          <t>-36.89587037866053,174.98789121465265</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -52204,6 +52344,132 @@
         </is>
       </c>
       <c r="H611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-36.89447953725321,174.98830529323487</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-36.89518365846212,174.98810695635416</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-36.89587384346293,174.98790840831327</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-36.89653092735589,174.98760532504429</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-36.89723329059083,174.9873832627757</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-36.897910413556936,174.98709938146212</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:12:13+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-36.89447920029025,174.98830286093843</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-36.895184835070246,174.98811547006315</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-36.89587239614072,174.98790122615108</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-36.89652497306605,174.9875850995784</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-36.89723512199425,174.98738947717445</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-36.897911572085434,174.98710266923428</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-36.89447984358311,174.98830750441346</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-36.89518515596326,174.9881177919838</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-36.895875795154296,174.98791809335063</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-36.89652943878376,174.98760026867754</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-36.89724151638319,174.98741117490798</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-36.8979103411489,174.98709917597637</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H614"/>
+  <dimension ref="A1:H615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18852,6 +18852,36 @@
       <c r="H614" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>213.16</v>
+      </c>
+      <c r="C615" t="n">
+        <v>215.34</v>
+      </c>
+      <c r="D615" t="n">
+        <v>215.41</v>
+      </c>
+      <c r="E615" t="n">
+        <v>223.48</v>
+      </c>
+      <c r="F615" t="n">
+        <v>212.09</v>
+      </c>
+      <c r="G615" t="n">
+        <v>208.93</v>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18866,7 +18896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26119,6 +26149,16 @@
       </c>
       <c r="B725" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -26281,28 +26321,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1660957204252783</v>
+        <v>-0.1717890425336461</v>
       </c>
       <c r="J2" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K2" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02217915487967015</v>
+        <v>0.02359503111752326</v>
       </c>
       <c r="M2" t="n">
-        <v>5.819387712809717</v>
+        <v>5.833929376550371</v>
       </c>
       <c r="N2" t="n">
-        <v>53.39493274182521</v>
+        <v>53.71366588322253</v>
       </c>
       <c r="O2" t="n">
-        <v>7.307183639530706</v>
+        <v>7.328960764202693</v>
       </c>
       <c r="P2" t="n">
-        <v>233.4264706041207</v>
+        <v>233.4976376805002</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26353,28 +26393,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5217054538269948</v>
+        <v>-0.5232700148825776</v>
       </c>
       <c r="J3" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K3" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2052185542059892</v>
+        <v>0.2066631533237117</v>
       </c>
       <c r="M3" t="n">
-        <v>5.576582666160881</v>
+        <v>5.573453262916476</v>
       </c>
       <c r="N3" t="n">
-        <v>46.27545639305084</v>
+        <v>46.23072673301129</v>
       </c>
       <c r="O3" t="n">
-        <v>6.802606588143315</v>
+        <v>6.799318107943715</v>
       </c>
       <c r="P3" t="n">
-        <v>233.6355120840051</v>
+        <v>233.6550692483503</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26425,28 +26465,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1880821721259331</v>
+        <v>0.1862407210826482</v>
       </c>
       <c r="J4" t="n">
+        <v>614</v>
+      </c>
+      <c r="K4" t="n">
         <v>613</v>
       </c>
-      <c r="K4" t="n">
-        <v>612</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04284996916237105</v>
+        <v>0.04214208334484337</v>
       </c>
       <c r="M4" t="n">
-        <v>4.445497661943725</v>
+        <v>4.44647596980584</v>
       </c>
       <c r="N4" t="n">
-        <v>34.68857841086513</v>
+        <v>34.67445563954321</v>
       </c>
       <c r="O4" t="n">
-        <v>5.88970104596703</v>
+        <v>5.888501986035431</v>
       </c>
       <c r="P4" t="n">
-        <v>215.4994389700358</v>
+        <v>215.5224681533533</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26497,28 +26537,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4031767241772629</v>
+        <v>0.4023994669886274</v>
       </c>
       <c r="J5" t="n">
+        <v>614</v>
+      </c>
+      <c r="K5" t="n">
         <v>613</v>
       </c>
-      <c r="K5" t="n">
-        <v>612</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1159951715519354</v>
+        <v>0.1159467758774146</v>
       </c>
       <c r="M5" t="n">
-        <v>5.516646951299938</v>
+        <v>5.510672071644667</v>
       </c>
       <c r="N5" t="n">
-        <v>53.88658791065538</v>
+        <v>53.8061356395856</v>
       </c>
       <c r="O5" t="n">
-        <v>7.340748457116303</v>
+        <v>7.335266569088379</v>
       </c>
       <c r="P5" t="n">
-        <v>214.8365508844996</v>
+        <v>214.8463104224012</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26569,28 +26609,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3120348589740151</v>
+        <v>0.3108414781076711</v>
       </c>
       <c r="J6" t="n">
+        <v>614</v>
+      </c>
+      <c r="K6" t="n">
         <v>613</v>
       </c>
-      <c r="K6" t="n">
-        <v>612</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04224473496919512</v>
+        <v>0.04207024840889684</v>
       </c>
       <c r="M6" t="n">
-        <v>7.524702594309456</v>
+        <v>7.517252161115247</v>
       </c>
       <c r="N6" t="n">
-        <v>96.0203405221804</v>
+        <v>95.88127252906979</v>
       </c>
       <c r="O6" t="n">
-        <v>9.798996914081584</v>
+        <v>9.791898310801118</v>
       </c>
       <c r="P6" t="n">
-        <v>207.0387237775128</v>
+        <v>207.0537083231259</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26641,28 +26681,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2037240486025845</v>
+        <v>-0.2032946864358779</v>
       </c>
       <c r="J7" t="n">
+        <v>614</v>
+      </c>
+      <c r="K7" t="n">
         <v>613</v>
       </c>
-      <c r="K7" t="n">
-        <v>612</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.06776161786297008</v>
+        <v>0.06771201901667112</v>
       </c>
       <c r="M7" t="n">
-        <v>3.932609297743701</v>
+        <v>3.928098187071609</v>
       </c>
       <c r="N7" t="n">
-        <v>24.83721321059429</v>
+        <v>24.79897036828556</v>
       </c>
       <c r="O7" t="n">
-        <v>4.983694734892406</v>
+        <v>4.979856460610643</v>
       </c>
       <c r="P7" t="n">
-        <v>213.1968827961525</v>
+        <v>213.1914915609207</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26700,7 +26740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H614"/>
+  <dimension ref="A1:H615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52475,6 +52515,48 @@
         </is>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-36.89447984358311,174.98830750441346</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-36.89518697435614,174.98813094953462</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-36.89587998361281,174.9879388780952</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-36.89653390449947,174.98761543777835</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-36.89724595520419,174.9874262369289</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-36.89791396155015,174.98710945026463</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H615"/>
+  <dimension ref="A1:H621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18880,6 +18880,186 @@
         <v>208.93</v>
       </c>
       <c r="H615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>213.62</v>
+      </c>
+      <c r="C616" t="n">
+        <v>215.49</v>
+      </c>
+      <c r="D616" t="n">
+        <v>216.07</v>
+      </c>
+      <c r="E616" t="n">
+        <v>223.84</v>
+      </c>
+      <c r="F616" t="n">
+        <v>212.37</v>
+      </c>
+      <c r="G616" t="n">
+        <v>209.11</v>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>220.03</v>
+      </c>
+      <c r="C617" t="n">
+        <v>218.03</v>
+      </c>
+      <c r="D617" t="n">
+        <v>219.14</v>
+      </c>
+      <c r="E617" t="n">
+        <v>226.21</v>
+      </c>
+      <c r="F617" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="G617" t="n">
+        <v>213.08</v>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>220.03</v>
+      </c>
+      <c r="C618" t="n">
+        <v>219.18</v>
+      </c>
+      <c r="D618" t="n">
+        <v>220.19</v>
+      </c>
+      <c r="E618" t="n">
+        <v>226.89</v>
+      </c>
+      <c r="F618" t="n">
+        <v>217.85</v>
+      </c>
+      <c r="G618" t="n">
+        <v>213.95</v>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:28+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>223.74</v>
+      </c>
+      <c r="C619" t="n">
+        <v>218.23</v>
+      </c>
+      <c r="D619" t="n">
+        <v>219.57</v>
+      </c>
+      <c r="E619" t="n">
+        <v>226.37</v>
+      </c>
+      <c r="F619" t="n">
+        <v>218.65</v>
+      </c>
+      <c r="G619" t="n">
+        <v>212.53</v>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>223.74</v>
+      </c>
+      <c r="C620" t="n">
+        <v>219.93</v>
+      </c>
+      <c r="D620" t="n">
+        <v>219.54</v>
+      </c>
+      <c r="E620" t="n">
+        <v>226.26</v>
+      </c>
+      <c r="F620" t="n">
+        <v>221.56</v>
+      </c>
+      <c r="G620" t="n">
+        <v>215.68</v>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>223.59</v>
+      </c>
+      <c r="C621" t="n">
+        <v>219.52</v>
+      </c>
+      <c r="D621" t="n">
+        <v>219.85</v>
+      </c>
+      <c r="E621" t="n">
+        <v>226.25</v>
+      </c>
+      <c r="F621" t="n">
+        <v>221.56</v>
+      </c>
+      <c r="G621" t="n">
+        <v>215.68</v>
+      </c>
+      <c r="H621" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18896,7 +19076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B726"/>
+  <dimension ref="A1:B732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26159,6 +26339,66 @@
       </c>
       <c r="B726" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -26321,28 +26561,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1717890425336461</v>
+        <v>-0.1888306129940552</v>
       </c>
       <c r="J2" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K2" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02359503111752326</v>
+        <v>0.02856139470268559</v>
       </c>
       <c r="M2" t="n">
-        <v>5.833929376550371</v>
+        <v>5.848386033301227</v>
       </c>
       <c r="N2" t="n">
-        <v>53.71366588322253</v>
+        <v>53.93548659312904</v>
       </c>
       <c r="O2" t="n">
-        <v>7.328960764202693</v>
+        <v>7.344078335171067</v>
       </c>
       <c r="P2" t="n">
-        <v>233.4976376805002</v>
+        <v>233.7110256082946</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26393,28 +26633,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5232700148825776</v>
+        <v>-0.5258648092047874</v>
       </c>
       <c r="J3" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K3" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2066631533237117</v>
+        <v>0.211611582739842</v>
       </c>
       <c r="M3" t="n">
-        <v>5.573453262916476</v>
+        <v>5.530491926441609</v>
       </c>
       <c r="N3" t="n">
-        <v>46.23072673301129</v>
+        <v>45.81871078079085</v>
       </c>
       <c r="O3" t="n">
-        <v>6.799318107943715</v>
+        <v>6.768951970637024</v>
       </c>
       <c r="P3" t="n">
-        <v>233.6550692483503</v>
+        <v>233.6875418019177</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26465,28 +26705,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1862407210826482</v>
+        <v>0.1831795573196744</v>
       </c>
       <c r="J4" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K4" t="n">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04214208334484337</v>
+        <v>0.04160165481697309</v>
       </c>
       <c r="M4" t="n">
-        <v>4.44647596980584</v>
+        <v>4.417104796118036</v>
       </c>
       <c r="N4" t="n">
-        <v>34.67445563954321</v>
+        <v>34.37652553508615</v>
       </c>
       <c r="O4" t="n">
-        <v>5.888501986035431</v>
+        <v>5.863149796405184</v>
       </c>
       <c r="P4" t="n">
-        <v>215.5224681533533</v>
+        <v>215.5608085721286</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26537,28 +26777,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4023994669886274</v>
+        <v>0.4031232784166964</v>
       </c>
       <c r="J5" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K5" t="n">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1159467758774146</v>
+        <v>0.1184614569709121</v>
       </c>
       <c r="M5" t="n">
-        <v>5.510672071644667</v>
+        <v>5.466654563313281</v>
       </c>
       <c r="N5" t="n">
-        <v>53.8061356395856</v>
+        <v>53.29488597809242</v>
       </c>
       <c r="O5" t="n">
-        <v>7.335266569088379</v>
+        <v>7.300334648363212</v>
       </c>
       <c r="P5" t="n">
-        <v>214.8463104224012</v>
+        <v>214.837189308861</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26609,28 +26849,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3108414781076711</v>
+        <v>0.3165872940918836</v>
       </c>
       <c r="J6" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K6" t="n">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04207024840889684</v>
+        <v>0.04437750813504204</v>
       </c>
       <c r="M6" t="n">
-        <v>7.517252161115247</v>
+        <v>7.48241904590757</v>
       </c>
       <c r="N6" t="n">
-        <v>95.88127252906979</v>
+        <v>95.1165215513862</v>
       </c>
       <c r="O6" t="n">
-        <v>9.791898310801118</v>
+        <v>9.752769942502807</v>
       </c>
       <c r="P6" t="n">
-        <v>207.0537083231259</v>
+        <v>206.9813362175901</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26681,28 +26921,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2032946864358779</v>
+        <v>-0.1914107896086403</v>
       </c>
       <c r="J7" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K7" t="n">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06771201901667112</v>
+        <v>0.06089381977934027</v>
       </c>
       <c r="M7" t="n">
-        <v>3.928098187071609</v>
+        <v>3.942577549325839</v>
       </c>
       <c r="N7" t="n">
-        <v>24.79897036828556</v>
+        <v>24.90117599849488</v>
       </c>
       <c r="O7" t="n">
-        <v>4.979856460610643</v>
+        <v>4.990107814315727</v>
       </c>
       <c r="P7" t="n">
-        <v>213.1914915609207</v>
+        <v>213.0419141493242</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26740,7 +26980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H615"/>
+  <dimension ref="A1:H621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52557,6 +52797,258 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-36.89447913902425,174.98830241870272</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-36.89518674514705,174.98812929101976</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-36.89587853629249,174.98793169593193</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-36.896532788070736,174.987611645503</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-36.89724508606457,174.9874232877219</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-36.897913309878,174.9871076008927</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-36.89446932112656,174.98823155043772</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-36.89518286386927,174.98810120683655</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>-36.89587180405423,174.9878982879939</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-36.89652543824508,174.98758667969284</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-36.89723226624641,174.98737978692566</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-36.89789893687893,174.98706681197436</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-36.89446932112656,174.98823155043772</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-36.895181106595615,174.98808849155756</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-36.89586950149497,174.98788686182738</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-36.896523329433336,174.98757951650762</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-36.89722807574539,174.98736556754008</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-36.897895787126565,174.9870578733469</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:28+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-36.894463638673216,174.9881905330874</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-36.89518255825656,174.98809899548363</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-36.89587086110152,174.98789360870657</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-36.896524942054114,174.98758499423747</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-36.897225592484695,174.9873571412382</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-36.89790092810133,174.98707246283118</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-36.894463638673216,174.9881905330874</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-36.895179960546834,174.98808019898462</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-36.89587092688894,174.98789393516847</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-36.896525283185404,174.98758615298803</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-36.89721655961875,174.9873264905696</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-36.89788952382383,174.9870400988369</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-36.89446386842227,174.98819219147074</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-36.89518058705358,174.9880847322578</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-36.8958702470857,174.98789056172885</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-36.89652531419734,174.98758625832897</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-36.89721655961875,174.9873264905696</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-36.89788952382383,174.9870400988369</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H621"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19054,14 +19054,134 @@
         <v>226.25</v>
       </c>
       <c r="F621" t="n">
+        <v>220.74</v>
+      </c>
+      <c r="G621" t="n">
+        <v>215.16</v>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>222.19</v>
+      </c>
+      <c r="C622" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="D622" t="n">
+        <v>218.11</v>
+      </c>
+      <c r="E622" t="n">
+        <v>225.85</v>
+      </c>
+      <c r="F622" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="G622" t="n">
+        <v>213.98</v>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>222.19</v>
+      </c>
+      <c r="C623" t="n">
+        <v>219.88</v>
+      </c>
+      <c r="D623" t="n">
+        <v>219.02</v>
+      </c>
+      <c r="E623" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="F623" t="n">
+        <v>220.04</v>
+      </c>
+      <c r="G623" t="n">
+        <v>213.58</v>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>223.22</v>
+      </c>
+      <c r="C624" t="n">
+        <v>218.82</v>
+      </c>
+      <c r="D624" t="n">
+        <v>219.48</v>
+      </c>
+      <c r="E624" t="n">
+        <v>225.72</v>
+      </c>
+      <c r="F624" t="n">
+        <v>223.26</v>
+      </c>
+      <c r="G624" t="n">
+        <v>213.88</v>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
         <v>221.56</v>
       </c>
-      <c r="G621" t="n">
-        <v>215.68</v>
-      </c>
-      <c r="H621" t="inlineStr">
-        <is>
-          <t>L8</t>
+      <c r="C625" t="n">
+        <v>216.93</v>
+      </c>
+      <c r="D625" t="n">
+        <v>217.93</v>
+      </c>
+      <c r="E625" t="n">
+        <v>224.46</v>
+      </c>
+      <c r="F625" t="n">
+        <v>223.82</v>
+      </c>
+      <c r="G625" t="n">
+        <v>213.08</v>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B732"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26399,6 +26519,46 @@
       </c>
       <c r="B732" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -26561,28 +26721,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1888306129940552</v>
+        <v>-0.1976345874690168</v>
       </c>
       <c r="J2" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K2" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02856139470268559</v>
+        <v>0.03147112519186712</v>
       </c>
       <c r="M2" t="n">
-        <v>5.848386033301227</v>
+        <v>5.847349498171225</v>
       </c>
       <c r="N2" t="n">
-        <v>53.93548659312904</v>
+        <v>53.84507015533965</v>
       </c>
       <c r="O2" t="n">
-        <v>7.344078335171067</v>
+        <v>7.337920015599765</v>
       </c>
       <c r="P2" t="n">
-        <v>233.7110256082946</v>
+        <v>233.8216304834642</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26633,28 +26793,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5258648092047874</v>
+        <v>-0.5274842753648146</v>
       </c>
       <c r="J3" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.211611582739842</v>
+        <v>0.2148701948269053</v>
       </c>
       <c r="M3" t="n">
-        <v>5.530491926441609</v>
+        <v>5.502257083789459</v>
       </c>
       <c r="N3" t="n">
-        <v>45.81871078079085</v>
+        <v>45.54115739268722</v>
       </c>
       <c r="O3" t="n">
-        <v>6.768951970637024</v>
+        <v>6.748418880944426</v>
       </c>
       <c r="P3" t="n">
-        <v>233.6875418019177</v>
+        <v>233.7078899550805</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26705,28 +26865,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1831795573196744</v>
+        <v>0.1806152585301324</v>
       </c>
       <c r="J4" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K4" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04160165481697309</v>
+        <v>0.04099665234626759</v>
       </c>
       <c r="M4" t="n">
-        <v>4.417104796118036</v>
+        <v>4.400078135161849</v>
       </c>
       <c r="N4" t="n">
-        <v>34.37652553508615</v>
+        <v>34.17992166232777</v>
       </c>
       <c r="O4" t="n">
-        <v>5.863149796405184</v>
+        <v>5.846359693204633</v>
       </c>
       <c r="P4" t="n">
-        <v>215.5608085721286</v>
+        <v>215.5930376700899</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26777,28 +26937,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4031232784166964</v>
+        <v>0.4024713318088057</v>
       </c>
       <c r="J5" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K5" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1184614569709121</v>
+        <v>0.1195508633968185</v>
       </c>
       <c r="M5" t="n">
-        <v>5.466654563313281</v>
+        <v>5.434949746271963</v>
       </c>
       <c r="N5" t="n">
-        <v>53.29488597809242</v>
+        <v>52.95634088550804</v>
       </c>
       <c r="O5" t="n">
-        <v>7.300334648363212</v>
+        <v>7.277110751219061</v>
       </c>
       <c r="P5" t="n">
-        <v>214.837189308861</v>
+        <v>214.8454199684474</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26849,28 +27009,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3165872940918836</v>
+        <v>0.3248850556904065</v>
       </c>
       <c r="J6" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K6" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04437750813504204</v>
+        <v>0.04712009797359806</v>
       </c>
       <c r="M6" t="n">
-        <v>7.48241904590757</v>
+        <v>7.474842617591261</v>
       </c>
       <c r="N6" t="n">
-        <v>95.1165215513862</v>
+        <v>94.75190804894083</v>
       </c>
       <c r="O6" t="n">
-        <v>9.752769942502807</v>
+        <v>9.73405917636321</v>
       </c>
       <c r="P6" t="n">
-        <v>206.9813362175901</v>
+        <v>206.8765954733237</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26921,28 +27081,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1914107896086403</v>
+        <v>-0.1835741011656172</v>
       </c>
       <c r="J7" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K7" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06089381977934027</v>
+        <v>0.05659503887525397</v>
       </c>
       <c r="M7" t="n">
-        <v>3.942577549325839</v>
+        <v>3.95173240107665</v>
       </c>
       <c r="N7" t="n">
-        <v>24.90117599849488</v>
+        <v>24.93670838210521</v>
       </c>
       <c r="O7" t="n">
-        <v>4.990107814315727</v>
+        <v>4.99366682730288</v>
       </c>
       <c r="P7" t="n">
-        <v>213.0419141493242</v>
+        <v>212.9430197609856</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26980,7 +27140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H621"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53035,17 +53195,185 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>-36.89721655961875,174.9873264905696</t>
+          <t>-36.89721910496324,174.98733512752705</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>-36.89788952382383,174.9870400988369</t>
+          <t>-36.89789140643535,174.9870454414639</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.89446601274576,174.98820766971556</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.895183031956236,174.98810242308065</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.89587406275413,174.9879094965197</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.89652655467463,174.98759047196748</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.89722326442725,174.9873492415807</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-36.89789567851441,174.9870575651184</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-36.89446601274576,174.98820766971556</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-36.8951800369501,174.9880807518228</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-36.89587206720378,174.98789959384152</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-36.89652981092681,174.9876015327692</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-36.89722127781779,174.98734250053994</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-36.89789712667652,174.98706167483206</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-36.894464435136534,174.98819628214966</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-36.89518165669882,174.98809247199264</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-36.89587105846374,174.98789458809227</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-36.89652695782972,174.98759184140005</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-36.89721128268298,174.9873085846839</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-36.89789604055494,174.9870585925468</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-36.89446697769066,174.988214634926</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-36.89518454473842,174.98811336927778</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-36.89587445747828,174.98791145529128</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-36.89653086533205,174.98760511436234</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-36.897209544397654,174.987302686275</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-36.89789893687893,174.98706681197436</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
